--- a/docs/downloads/经营分_津河省区__津南片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_津河省区__津南片区_2026-10-18.xlsx
@@ -797,7 +797,7 @@
         <v>70</v>
       </c>
       <c r="I3" t="n">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>70</v>
       </c>
       <c r="I4" t="n">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>7301176193271728137</t>
+          <t>7028040302908672000</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津国家会展中心星光大道店)</t>
+          <t>麗枫酒店天津梅江会展复兴门地铁站店</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津国家会展中心星光大道店)</t>
+          <t>麗枫酒店(天津梅江会展复兴门地铁站店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1226,36 +1226,36 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I8" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N8" t="n">
         <v>30</v>
       </c>
       <c r="O8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P8" t="n">
         <v>30</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
         <v>30</v>
@@ -1295,17 +1295,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7028040302908672000</t>
+          <t>7373180892628158505</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>麗枫酒店天津梅江会展复兴门地铁站店</t>
+          <t>7天酒店·天津津南北闸口镇店</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津梅江会展复兴门地铁站店)</t>
+          <t>7天酒店(天津津南北闸口镇店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1314,24 +1314,24 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
@@ -1383,29 +1383,29 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>7373180892628158505</t>
+          <t>6601138347408623630</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7天酒店·天津津南北闸口镇店</t>
+          <t>派酒店（天津宾馆地铁站市政府店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7天酒店(天津津南北闸口镇店)</t>
+          <t>派酒店(天津宾馆地铁站市政府店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>85</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1471,17 +1471,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6601138347408623630</t>
+          <t>6601131530519578632</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>派酒店（天津宾馆地铁站市政府店）</t>
+          <t>7天酒店（天津奥体中心肿瘤医院地铁站）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>派酒店(天津宾馆地铁站市政府店)</t>
+          <t>7天酒店(天津肿瘤医院地铁站店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N11" t="n">
         <v>30</v>
@@ -1519,7 +1519,7 @@
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
         <v>30</v>
@@ -1559,17 +1559,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>6601131530519578632</t>
+          <t>7371773508466804772</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7天酒店（天津奥体中心肿瘤医院地铁站）</t>
+          <t>希岸酒店天津奥体中心肿瘤医院地铁站店</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>7天酒店(天津肿瘤医院地铁站店)</t>
+          <t>希岸酒店(天津奥体中心肿瘤医院地铁站店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1581,7 +1581,7 @@
         <v>87</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N12" t="n">
         <v>30</v>
@@ -1607,7 +1607,7 @@
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R12" t="n">
         <v>30</v>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>7371773508466804772</t>
+          <t>7045846491030390819</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>希岸酒店天津奥体中心肿瘤医院地铁站店</t>
+          <t>维也纳国际酒店（天津国展吾悦广场店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>希岸酒店(天津奥体中心肿瘤医院地铁站店)</t>
+          <t>维也纳国际酒店(天津国展吾悦广场店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1669,7 +1669,7 @@
         <v>87</v>
       </c>
       <c r="I13" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1735,17 +1735,17 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7045846491030390819</t>
+          <t>7301176193271728137</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（天津国展吾悦广场店）</t>
+          <t>维也纳酒店(天津国家会展中心星光大道店)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(天津国展吾悦广场店)</t>
+          <t>维也纳酒店(天津国家会展中心星光大道店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1777,13 +1777,13 @@
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P14" t="n">
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -2175,17 +2175,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7524979893952579599</t>
+          <t>7088949461086390303</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>天津梅江会展中心锦江都城酒店</t>
+          <t>麗枫酒店（天津站五大道景区店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>天津梅江会展中心锦江都城酒店</t>
+          <t>麗枫酒店(天津站五大道景区店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2197,11 +2197,11 @@
         <v>92</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2211,19 +2211,19 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2263,17 +2263,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7088949461086390303</t>
+          <t>7066985349183965225</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>麗枫酒店（天津站五大道景区店）</t>
+          <t>维也纳酒店（天津津南领世郡双港地铁站店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津站五大道景区店)</t>
+          <t>维也纳酒店(天津津南领世郡双港地铁站店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2282,24 +2282,24 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
@@ -2351,49 +2351,49 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7066985349183965225</t>
+          <t>6601137735086376973</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>维也纳酒店（天津津南领世郡双港地铁站店）</t>
+          <t>IU酒店 天津五大道吴家窑地铁站店</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津津南领世郡双港地铁站店)</t>
+          <t>iu酒店(天津天塔景区吴家窑地铁站店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L21" t="n">
         <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
         <v>30</v>
       </c>
       <c r="O21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P21" t="n">
         <v>30</v>
@@ -2439,17 +2439,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>6601137735086376973</t>
+          <t>7524979893952579599</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IU酒店 天津五大道吴家窑地铁站店</t>
+          <t>天津梅江会展中心锦江都城酒店</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>iu酒店(天津天塔景区吴家窑地铁站店)</t>
+          <t>天津梅江会展中心锦江都城酒店</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2458,14 +2458,14 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -2475,19 +2475,19 @@
         <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N22" t="n">
         <v>30</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P22" t="n">
         <v>30</v>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R22" t="n">
         <v>30</v>
@@ -2637,7 +2637,7 @@
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H28" t="n">
